--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128719848</v>
       </c>
       <c r="B2" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128720056</v>
       </c>
       <c r="B3" t="n">
-        <v>91939</v>
+        <v>91940</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>128720334</v>
       </c>
       <c r="B4" t="n">
-        <v>92232</v>
+        <v>92233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128720007</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>128720161</v>
       </c>
       <c r="B6" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,6 +1298,3271 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128813827</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>321650</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6581051</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128813503</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>321927</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6581186</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128813811</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>321718</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6581068</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128812360</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91487</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>321721</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6581075</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128814748</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>321686</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6581116</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128814786</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>321762</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6581081</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128813685</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>321760</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6581086</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128813559</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>321769</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6581082</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128812889</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>321697</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6581046</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Ljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Brandstubbe # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128814567</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>321649</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6581085</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128813792</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>321756</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6581052</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128813756</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>321760</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6581080</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128813609</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>321774</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6581096</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128813491</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>321933</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6581182</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128812572</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>321691</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6581080</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128813781</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>321751</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6581060</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128813570</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>321769</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6581094</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128814510</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>321644</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6581080</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128813875</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>321541</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6581033</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128813533</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>321778</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6581074</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128813944</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>321551</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6581045</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128813543</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>321774</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6581075</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128814795</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>321915</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6581155</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128814801</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>321969</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6581188</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128814805</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>321973</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6581193</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128814494</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>321602</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6581078</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128814762</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>321771</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6581097</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128813918</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>321544</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6581038</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128813958</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>321545</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6581041</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128719848</v>
       </c>
       <c r="B2" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128720056</v>
       </c>
       <c r="B3" t="n">
-        <v>91940</v>
+        <v>91967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>128720334</v>
       </c>
       <c r="B4" t="n">
-        <v>92233</v>
+        <v>92260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128720007</v>
       </c>
       <c r="B5" t="n">
-        <v>92088</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>128720161</v>
       </c>
       <c r="B6" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128813827</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>128813503</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128813811</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128812360</v>
       </c>
       <c r="B10" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128814748</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128814786</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>128813685</v>
       </c>
       <c r="B13" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128813559</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>128812889</v>
       </c>
       <c r="B15" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814567</v>
+        <v>128813792</v>
       </c>
       <c r="B16" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,14 +2371,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>321649</v>
+        <v>321756</v>
       </c>
       <c r="R16" t="n">
-        <v>6581085</v>
+        <v>6581052</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2443,10 +2443,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128813792</v>
+        <v>128814567</v>
       </c>
       <c r="B17" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,14 +2482,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>321756</v>
+        <v>321649</v>
       </c>
       <c r="R17" t="n">
-        <v>6581052</v>
+        <v>6581085</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2557,7 +2557,7 @@
         <v>128813756</v>
       </c>
       <c r="B18" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,53 +2665,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128813609</v>
+        <v>128812572</v>
       </c>
       <c r="B19" t="n">
-        <v>98592</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>321774</v>
+        <v>321691</v>
       </c>
       <c r="R19" t="n">
-        <v>6581096</v>
+        <v>6581080</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2758,7 +2757,22 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2776,10 +2790,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128813491</v>
+        <v>128813609</v>
       </c>
       <c r="B20" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,10 +2833,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>321933</v>
+        <v>321774</v>
       </c>
       <c r="R20" t="n">
-        <v>6581182</v>
+        <v>6581096</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2887,52 +2901,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128812572</v>
+        <v>128813491</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>98619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>321691</v>
+        <v>321933</v>
       </c>
       <c r="R21" t="n">
-        <v>6581080</v>
+        <v>6581182</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2979,22 +2994,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128813781</v>
+        <v>128814510</v>
       </c>
       <c r="B22" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,14 +3051,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>321751</v>
+        <v>321644</v>
       </c>
       <c r="R22" t="n">
-        <v>6581060</v>
+        <v>6581080</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128813570</v>
+        <v>128813781</v>
       </c>
       <c r="B23" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>321769</v>
+        <v>321751</v>
       </c>
       <c r="R23" t="n">
-        <v>6581094</v>
+        <v>6581060</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128814510</v>
+        <v>128813570</v>
       </c>
       <c r="B24" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3273,14 +3273,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>321644</v>
+        <v>321769</v>
       </c>
       <c r="R24" t="n">
-        <v>6581080</v>
+        <v>6581094</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3348,7 +3348,7 @@
         <v>128813875</v>
       </c>
       <c r="B25" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>128813533</v>
       </c>
       <c r="B26" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>128813944</v>
       </c>
       <c r="B27" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128813543</v>
       </c>
       <c r="B28" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>128814795</v>
       </c>
       <c r="B29" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128814801</v>
       </c>
       <c r="B30" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128814805</v>
       </c>
       <c r="B31" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>128814494</v>
       </c>
       <c r="B32" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128814762</v>
       </c>
       <c r="B33" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128813918</v>
       </c>
       <c r="B34" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128813958</v>
       </c>
       <c r="B35" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4563,6 +4563,139 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128826818</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56907</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skansen O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>321835</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6581095</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Utflygande från stor tall.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -2332,7 +2332,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128813792</v>
+        <v>128814567</v>
       </c>
       <c r="B16" t="n">
         <v>98619</v>
@@ -2371,14 +2371,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>321756</v>
+        <v>321649</v>
       </c>
       <c r="R16" t="n">
-        <v>6581052</v>
+        <v>6581085</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128814567</v>
+        <v>128813792</v>
       </c>
       <c r="B17" t="n">
         <v>98619</v>
@@ -2482,14 +2482,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>321649</v>
+        <v>321756</v>
       </c>
       <c r="R17" t="n">
-        <v>6581085</v>
+        <v>6581052</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719848</v>
       </c>
       <c r="B2" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128720056</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>91972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>128720334</v>
       </c>
       <c r="B4" t="n">
-        <v>92260</v>
+        <v>92265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128720007</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>128720161</v>
       </c>
       <c r="B6" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128813827</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>128813503</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128813811</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128812360</v>
       </c>
       <c r="B10" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128814748</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128814786</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>128813685</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128813559</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>128812889</v>
       </c>
       <c r="B15" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>128814567</v>
       </c>
       <c r="B16" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>128813792</v>
       </c>
       <c r="B17" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128813756</v>
       </c>
       <c r="B18" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128812572</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>128813609</v>
       </c>
       <c r="B20" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>128813491</v>
       </c>
       <c r="B21" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128814510</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>128813781</v>
       </c>
       <c r="B23" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128813570</v>
       </c>
       <c r="B24" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3345,10 +3345,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128813875</v>
+        <v>128813533</v>
       </c>
       <c r="B25" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,14 +3384,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>321541</v>
+        <v>321778</v>
       </c>
       <c r="R25" t="n">
-        <v>6581033</v>
+        <v>6581074</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128813533</v>
+        <v>128813875</v>
       </c>
       <c r="B26" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,14 +3495,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>321778</v>
+        <v>321541</v>
       </c>
       <c r="R26" t="n">
-        <v>6581074</v>
+        <v>6581033</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3570,7 +3570,7 @@
         <v>128813944</v>
       </c>
       <c r="B27" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128813543</v>
       </c>
       <c r="B28" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>128814795</v>
       </c>
       <c r="B29" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128814801</v>
       </c>
       <c r="B30" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128814805</v>
       </c>
       <c r="B31" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>128814494</v>
       </c>
       <c r="B32" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128814762</v>
       </c>
       <c r="B33" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128813918</v>
       </c>
       <c r="B34" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128813958</v>
       </c>
       <c r="B35" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719848</v>
       </c>
       <c r="B2" t="n">
-        <v>96871</v>
+        <v>96878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128720056</v>
       </c>
       <c r="B3" t="n">
-        <v>91972</v>
+        <v>91977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>128720334</v>
       </c>
       <c r="B4" t="n">
-        <v>92265</v>
+        <v>92270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128720007</v>
       </c>
       <c r="B5" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>128720161</v>
       </c>
       <c r="B6" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128813827</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>128813503</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128813811</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128812360</v>
       </c>
       <c r="B10" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128814748</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128814786</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>128813685</v>
       </c>
       <c r="B13" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128813559</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>128814567</v>
       </c>
       <c r="B16" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>128813792</v>
       </c>
       <c r="B17" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128813756</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>128813609</v>
       </c>
       <c r="B20" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>128813491</v>
       </c>
       <c r="B21" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128814510</v>
       </c>
       <c r="B22" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>128813781</v>
       </c>
       <c r="B23" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128813570</v>
       </c>
       <c r="B24" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3345,10 +3345,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128813533</v>
+        <v>128813875</v>
       </c>
       <c r="B25" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,14 +3384,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>321778</v>
+        <v>321541</v>
       </c>
       <c r="R25" t="n">
-        <v>6581074</v>
+        <v>6581033</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128813875</v>
+        <v>128813533</v>
       </c>
       <c r="B26" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,14 +3495,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>321541</v>
+        <v>321778</v>
       </c>
       <c r="R26" t="n">
-        <v>6581033</v>
+        <v>6581074</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3570,7 +3570,7 @@
         <v>128813944</v>
       </c>
       <c r="B27" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128813543</v>
       </c>
       <c r="B28" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>128814795</v>
       </c>
       <c r="B29" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128814801</v>
       </c>
       <c r="B30" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128814805</v>
       </c>
       <c r="B31" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>128814494</v>
       </c>
       <c r="B32" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128814762</v>
       </c>
       <c r="B33" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128813918</v>
       </c>
       <c r="B34" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128813958</v>
       </c>
       <c r="B35" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -2665,52 +2665,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128812572</v>
+        <v>128813609</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>321691</v>
+        <v>321774</v>
       </c>
       <c r="R19" t="n">
-        <v>6581080</v>
+        <v>6581096</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2757,22 +2758,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2790,7 +2776,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128813609</v>
+        <v>128813491</v>
       </c>
       <c r="B20" t="n">
         <v>98632</v>
@@ -2833,10 +2819,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>321774</v>
+        <v>321933</v>
       </c>
       <c r="R20" t="n">
-        <v>6581096</v>
+        <v>6581182</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2901,53 +2887,52 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128813491</v>
+        <v>128812572</v>
       </c>
       <c r="B21" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>321933</v>
+        <v>321691</v>
       </c>
       <c r="R21" t="n">
-        <v>6581182</v>
+        <v>6581080</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2994,7 +2979,22 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719848</v>
       </c>
       <c r="B2" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128720056</v>
       </c>
       <c r="B3" t="n">
-        <v>91977</v>
+        <v>91981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>128720334</v>
       </c>
       <c r="B4" t="n">
-        <v>92270</v>
+        <v>92274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128720007</v>
       </c>
       <c r="B5" t="n">
-        <v>92125</v>
+        <v>92129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>128720161</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128813827</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>128813503</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128813811</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128812360</v>
       </c>
       <c r="B10" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128814748</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128814786</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>128813685</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128813559</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>128812889</v>
       </c>
       <c r="B15" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>128814567</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>128813792</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128813756</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,53 +2665,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128813609</v>
+        <v>128812572</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>321774</v>
+        <v>321691</v>
       </c>
       <c r="R19" t="n">
-        <v>6581096</v>
+        <v>6581080</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2758,7 +2757,22 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2776,10 +2790,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128813491</v>
+        <v>128813609</v>
       </c>
       <c r="B20" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,10 +2833,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>321933</v>
+        <v>321774</v>
       </c>
       <c r="R20" t="n">
-        <v>6581182</v>
+        <v>6581096</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2887,52 +2901,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128812572</v>
+        <v>128813491</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>321691</v>
+        <v>321933</v>
       </c>
       <c r="R21" t="n">
-        <v>6581080</v>
+        <v>6581182</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2979,22 +2994,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3015,7 +3015,7 @@
         <v>128814510</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>128813781</v>
       </c>
       <c r="B23" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128813570</v>
       </c>
       <c r="B24" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128813875</v>
       </c>
       <c r="B25" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>128813533</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>128813944</v>
       </c>
       <c r="B27" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128813543</v>
+        <v>128814795</v>
       </c>
       <c r="B28" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>321774</v>
+        <v>321915</v>
       </c>
       <c r="R28" t="n">
-        <v>6581075</v>
+        <v>6581155</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814795</v>
+        <v>128813543</v>
       </c>
       <c r="B29" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>321915</v>
+        <v>321774</v>
       </c>
       <c r="R29" t="n">
-        <v>6581155</v>
+        <v>6581075</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3903,7 +3903,7 @@
         <v>128814801</v>
       </c>
       <c r="B30" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128814805</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>128814494</v>
       </c>
       <c r="B32" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128814762</v>
       </c>
       <c r="B33" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128813918</v>
       </c>
       <c r="B34" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128813958</v>
       </c>
       <c r="B35" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>128826818</v>
       </c>
       <c r="B36" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -3678,7 +3678,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128814795</v>
+        <v>128813543</v>
       </c>
       <c r="B28" t="n">
         <v>98636</v>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>321915</v>
+        <v>321774</v>
       </c>
       <c r="R28" t="n">
-        <v>6581155</v>
+        <v>6581075</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3789,7 +3789,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128813543</v>
+        <v>128814795</v>
       </c>
       <c r="B29" t="n">
         <v>98636</v>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>321774</v>
+        <v>321915</v>
       </c>
       <c r="R29" t="n">
-        <v>6581075</v>
+        <v>6581155</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -2790,7 +2790,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128813609</v>
+        <v>128813491</v>
       </c>
       <c r="B20" t="n">
         <v>98636</v>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>321774</v>
+        <v>321933</v>
       </c>
       <c r="R20" t="n">
-        <v>6581096</v>
+        <v>6581182</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2901,7 +2901,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128813491</v>
+        <v>128813609</v>
       </c>
       <c r="B21" t="n">
         <v>98636</v>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>321933</v>
+        <v>321774</v>
       </c>
       <c r="R21" t="n">
-        <v>6581182</v>
+        <v>6581096</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128814510</v>
+        <v>128813781</v>
       </c>
       <c r="B22" t="n">
         <v>98636</v>
@@ -3051,14 +3051,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>321644</v>
+        <v>321751</v>
       </c>
       <c r="R22" t="n">
-        <v>6581080</v>
+        <v>6581060</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128813781</v>
+        <v>128814510</v>
       </c>
       <c r="B23" t="n">
         <v>98636</v>
@@ -3162,14 +3162,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>321751</v>
+        <v>321644</v>
       </c>
       <c r="R23" t="n">
-        <v>6581060</v>
+        <v>6581080</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3900,7 +3900,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814801</v>
+        <v>128814805</v>
       </c>
       <c r="B30" t="n">
         <v>98636</v>
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>321969</v>
+        <v>321973</v>
       </c>
       <c r="R30" t="n">
-        <v>6581188</v>
+        <v>6581193</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4011,7 +4011,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128814805</v>
+        <v>128814494</v>
       </c>
       <c r="B31" t="n">
         <v>98636</v>
@@ -4050,14 +4050,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>321973</v>
+        <v>321602</v>
       </c>
       <c r="R31" t="n">
-        <v>6581193</v>
+        <v>6581078</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4122,7 +4122,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128814494</v>
+        <v>128814801</v>
       </c>
       <c r="B32" t="n">
         <v>98636</v>
@@ -4161,14 +4161,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>321602</v>
+        <v>321969</v>
       </c>
       <c r="R32" t="n">
-        <v>6581078</v>
+        <v>6581188</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719848</v>
       </c>
       <c r="B2" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128720056</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
+        <v>91986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>128720334</v>
       </c>
       <c r="B4" t="n">
-        <v>92274</v>
+        <v>92279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128720007</v>
       </c>
       <c r="B5" t="n">
-        <v>92129</v>
+        <v>92134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>128720161</v>
       </c>
       <c r="B6" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128813827</v>
+        <v>128813503</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321650</v>
+        <v>321927</v>
       </c>
       <c r="R7" t="n">
-        <v>6581051</v>
+        <v>6581186</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128813503</v>
+        <v>128813827</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321927</v>
+        <v>321650</v>
       </c>
       <c r="R8" t="n">
-        <v>6581186</v>
+        <v>6581051</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1526,7 +1526,7 @@
         <v>128813811</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128812360</v>
       </c>
       <c r="B10" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128814748</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128814786</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>128813685</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128813559</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>128812889</v>
       </c>
       <c r="B15" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>128814567</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>128813792</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128813756</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,52 +2665,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128812572</v>
+        <v>128813609</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>98643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>321691</v>
+        <v>321774</v>
       </c>
       <c r="R19" t="n">
-        <v>6581080</v>
+        <v>6581096</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2757,22 +2758,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2790,53 +2776,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128813491</v>
+        <v>128812572</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>321933</v>
+        <v>321691</v>
       </c>
       <c r="R20" t="n">
-        <v>6581182</v>
+        <v>6581080</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2883,7 +2868,22 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128813609</v>
+        <v>128813491</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>321774</v>
+        <v>321933</v>
       </c>
       <c r="R21" t="n">
-        <v>6581096</v>
+        <v>6581182</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3015,7 +3015,7 @@
         <v>128813781</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>128814510</v>
       </c>
       <c r="B23" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128813570</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128813875</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>128813533</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>128813944</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128813543</v>
       </c>
       <c r="B28" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>128814795</v>
       </c>
       <c r="B29" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3900,10 +3900,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814805</v>
+        <v>128814494</v>
       </c>
       <c r="B30" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,14 +3939,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>321973</v>
+        <v>321602</v>
       </c>
       <c r="R30" t="n">
-        <v>6581193</v>
+        <v>6581078</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128814494</v>
+        <v>128814805</v>
       </c>
       <c r="B31" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,14 +4050,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>321602</v>
+        <v>321973</v>
       </c>
       <c r="R31" t="n">
-        <v>6581078</v>
+        <v>6581193</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4125,7 +4125,7 @@
         <v>128814801</v>
       </c>
       <c r="B32" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128814762</v>
       </c>
       <c r="B33" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128813918</v>
       </c>
       <c r="B34" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128813958</v>
       </c>
       <c r="B35" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>128826818</v>
       </c>
       <c r="B36" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719848</v>
       </c>
       <c r="B2" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128720056</v>
       </c>
       <c r="B3" t="n">
-        <v>91994</v>
+        <v>91997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>128720334</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128720007</v>
       </c>
       <c r="B5" t="n">
-        <v>92142</v>
+        <v>92147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>128720161</v>
       </c>
       <c r="B6" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128813827</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>128813503</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128813811</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128812360</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128814748</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128814786</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>128813685</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128813559</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>128814567</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>128813792</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128813756</v>
       </c>
       <c r="B18" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>128813609</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>128813491</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128814510</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>128813781</v>
       </c>
       <c r="B23" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128813570</v>
       </c>
       <c r="B24" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128813875</v>
       </c>
       <c r="B25" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>128813533</v>
       </c>
       <c r="B26" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>128813944</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128813543</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>128814795</v>
       </c>
       <c r="B29" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128814801</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128814805</v>
       </c>
       <c r="B31" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>128814494</v>
       </c>
       <c r="B32" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128814762</v>
       </c>
       <c r="B33" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128813918</v>
       </c>
       <c r="B34" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128813958</v>
       </c>
       <c r="B35" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719848</v>
       </c>
       <c r="B2" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128720056</v>
       </c>
       <c r="B3" t="n">
-        <v>91997</v>
+        <v>92000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>128720334</v>
       </c>
       <c r="B4" t="n">
-        <v>92292</v>
+        <v>92295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128720007</v>
       </c>
       <c r="B5" t="n">
-        <v>92147</v>
+        <v>92150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>128720161</v>
       </c>
       <c r="B6" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128813827</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>128813503</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128813811</v>
       </c>
       <c r="B9" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128812360</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128814748</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128814786</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>128813685</v>
       </c>
       <c r="B13" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128813559</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,41 +2207,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128812889</v>
+        <v>128814567</v>
       </c>
       <c r="B15" t="n">
-        <v>79653</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2249,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>321697</v>
+        <v>321649</v>
       </c>
       <c r="R15" t="n">
-        <v>6581046</v>
+        <v>6581085</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2299,22 +2300,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Ljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Brandstubbe # Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2332,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814567</v>
+        <v>128813792</v>
       </c>
       <c r="B16" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,14 +2357,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>321649</v>
+        <v>321756</v>
       </c>
       <c r="R16" t="n">
-        <v>6581085</v>
+        <v>6581052</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2443,53 +2429,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128813792</v>
+        <v>128812889</v>
       </c>
       <c r="B17" t="n">
-        <v>98656</v>
+        <v>79654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>321756</v>
+        <v>321697</v>
       </c>
       <c r="R17" t="n">
-        <v>6581052</v>
+        <v>6581046</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2536,7 +2521,22 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Ljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Brandstubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2557,7 +2557,7 @@
         <v>128813756</v>
       </c>
       <c r="B18" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128812572</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>128813609</v>
       </c>
       <c r="B20" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>128813491</v>
       </c>
       <c r="B21" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128814510</v>
       </c>
       <c r="B22" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>128813781</v>
       </c>
       <c r="B23" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128813570</v>
       </c>
       <c r="B24" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128813875</v>
       </c>
       <c r="B25" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>128813533</v>
       </c>
       <c r="B26" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>128813944</v>
       </c>
       <c r="B27" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128813543</v>
       </c>
       <c r="B28" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>128814795</v>
       </c>
       <c r="B29" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128814801</v>
       </c>
       <c r="B30" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128814805</v>
       </c>
       <c r="B31" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>128814494</v>
       </c>
       <c r="B32" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128814762</v>
       </c>
       <c r="B33" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128813918</v>
       </c>
       <c r="B34" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128813958</v>
       </c>
       <c r="B35" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -2207,42 +2207,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128814567</v>
+        <v>128812889</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>79654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2250,10 +2249,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>321649</v>
+        <v>321697</v>
       </c>
       <c r="R15" t="n">
-        <v>6581085</v>
+        <v>6581046</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2300,7 +2299,22 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Ljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Brandstubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2318,7 +2332,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128813792</v>
+        <v>128814567</v>
       </c>
       <c r="B16" t="n">
         <v>98659</v>
@@ -2357,14 +2371,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>321756</v>
+        <v>321649</v>
       </c>
       <c r="R16" t="n">
-        <v>6581052</v>
+        <v>6581085</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2429,52 +2443,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128812889</v>
+        <v>128813792</v>
       </c>
       <c r="B17" t="n">
-        <v>79654</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>321697</v>
+        <v>321756</v>
       </c>
       <c r="R17" t="n">
-        <v>6581046</v>
+        <v>6581052</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2521,22 +2536,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Ljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Brandstubbe # Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -2207,41 +2207,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128812889</v>
+        <v>128814567</v>
       </c>
       <c r="B15" t="n">
-        <v>79654</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2249,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>321697</v>
+        <v>321649</v>
       </c>
       <c r="R15" t="n">
-        <v>6581046</v>
+        <v>6581085</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2299,22 +2300,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Ljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Brandstubbe # Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2332,7 +2318,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814567</v>
+        <v>128813792</v>
       </c>
       <c r="B16" t="n">
         <v>98659</v>
@@ -2371,14 +2357,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>321649</v>
+        <v>321756</v>
       </c>
       <c r="R16" t="n">
-        <v>6581085</v>
+        <v>6581052</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2443,53 +2429,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128813792</v>
+        <v>128812889</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>79654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>321756</v>
+        <v>321697</v>
       </c>
       <c r="R17" t="n">
-        <v>6581052</v>
+        <v>6581046</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2536,7 +2521,22 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Ljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Brandstubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719848</v>
       </c>
       <c r="B2" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128720056</v>
       </c>
       <c r="B3" t="n">
-        <v>92000</v>
+        <v>92007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>128720334</v>
       </c>
       <c r="B4" t="n">
-        <v>92295</v>
+        <v>92302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128720007</v>
       </c>
       <c r="B5" t="n">
-        <v>92150</v>
+        <v>92157</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>128720161</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128813827</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>128813503</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128813811</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128812360</v>
       </c>
       <c r="B10" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128814748</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128814786</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>128813685</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128813559</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>128812889</v>
       </c>
       <c r="B15" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>128814567</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>128813792</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128813756</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,52 +2665,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128812572</v>
+        <v>128813609</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>321691</v>
+        <v>321774</v>
       </c>
       <c r="R19" t="n">
-        <v>6581080</v>
+        <v>6581096</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2757,22 +2758,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2790,53 +2776,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128813609</v>
+        <v>128812572</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>321774</v>
+        <v>321691</v>
       </c>
       <c r="R20" t="n">
-        <v>6581096</v>
+        <v>6581080</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2883,7 +2868,22 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         <v>128813491</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128814510</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>128813781</v>
       </c>
       <c r="B23" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128813570</v>
       </c>
       <c r="B24" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128813875</v>
       </c>
       <c r="B25" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>128813533</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>128813944</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128813543</v>
+        <v>128814795</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>321774</v>
+        <v>321915</v>
       </c>
       <c r="R28" t="n">
-        <v>6581075</v>
+        <v>6581155</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814795</v>
+        <v>128813543</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>321915</v>
+        <v>321774</v>
       </c>
       <c r="R29" t="n">
-        <v>6581155</v>
+        <v>6581075</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3903,7 +3903,7 @@
         <v>128814801</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128814805</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>128814494</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128814762</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128813918</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128813958</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>128826818</v>
       </c>
       <c r="B36" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -3678,7 +3678,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128814795</v>
+        <v>128813543</v>
       </c>
       <c r="B28" t="n">
         <v>98669</v>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>321915</v>
+        <v>321774</v>
       </c>
       <c r="R28" t="n">
-        <v>6581155</v>
+        <v>6581075</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3789,7 +3789,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128813543</v>
+        <v>128814795</v>
       </c>
       <c r="B29" t="n">
         <v>98669</v>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>321774</v>
+        <v>321915</v>
       </c>
       <c r="R29" t="n">
-        <v>6581075</v>
+        <v>6581155</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -1304,7 +1304,7 @@
         <v>128813827</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>128813503</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128813811</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128812360</v>
       </c>
       <c r="B10" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128814748</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128814786</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>128813685</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128813559</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>128814567</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>128813792</v>
       </c>
       <c r="B17" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128813756</v>
       </c>
       <c r="B18" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,53 +2665,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128813609</v>
+        <v>128812572</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>321774</v>
+        <v>321691</v>
       </c>
       <c r="R19" t="n">
-        <v>6581096</v>
+        <v>6581080</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2758,7 +2757,22 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2776,52 +2790,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128812572</v>
+        <v>128813609</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>321691</v>
+        <v>321774</v>
       </c>
       <c r="R20" t="n">
-        <v>6581080</v>
+        <v>6581096</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2868,22 +2883,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         <v>128813491</v>
       </c>
       <c r="B21" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128814510</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>128813781</v>
       </c>
       <c r="B23" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128813570</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128813875</v>
       </c>
       <c r="B25" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>128813533</v>
       </c>
       <c r="B26" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>128813944</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128813543</v>
       </c>
       <c r="B28" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>128814795</v>
       </c>
       <c r="B29" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128814801</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128814805</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>128814494</v>
       </c>
       <c r="B32" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128814762</v>
       </c>
       <c r="B33" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128813918</v>
       </c>
       <c r="B34" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128813958</v>
       </c>
       <c r="B35" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719848</v>
       </c>
       <c r="B2" t="n">
-        <v>96915</v>
+        <v>96924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128720056</v>
       </c>
       <c r="B3" t="n">
-        <v>92007</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>128720334</v>
       </c>
       <c r="B4" t="n">
-        <v>92302</v>
+        <v>92311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128720007</v>
       </c>
       <c r="B5" t="n">
-        <v>92157</v>
+        <v>92166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>128720161</v>
       </c>
       <c r="B6" t="n">
-        <v>91533</v>
+        <v>91542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128813827</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>128813503</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128813811</v>
       </c>
       <c r="B9" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128812360</v>
       </c>
       <c r="B10" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128814748</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128814786</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>128813685</v>
       </c>
       <c r="B13" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128813559</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>128812889</v>
       </c>
       <c r="B15" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>128814567</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>128813792</v>
       </c>
       <c r="B17" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128813756</v>
       </c>
       <c r="B18" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,52 +2665,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128812572</v>
+        <v>128813609</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>321691</v>
+        <v>321774</v>
       </c>
       <c r="R19" t="n">
-        <v>6581080</v>
+        <v>6581096</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2757,22 +2758,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2790,10 +2776,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128813609</v>
+        <v>128813491</v>
       </c>
       <c r="B20" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,10 +2819,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>321774</v>
+        <v>321933</v>
       </c>
       <c r="R20" t="n">
-        <v>6581096</v>
+        <v>6581182</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2901,53 +2887,52 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128813491</v>
+        <v>128812572</v>
       </c>
       <c r="B21" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>321933</v>
+        <v>321691</v>
       </c>
       <c r="R21" t="n">
-        <v>6581182</v>
+        <v>6581080</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2994,7 +2979,22 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3015,7 +3015,7 @@
         <v>128814510</v>
       </c>
       <c r="B22" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>128813781</v>
       </c>
       <c r="B23" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128813570</v>
       </c>
       <c r="B24" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128813875</v>
       </c>
       <c r="B25" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>128813533</v>
       </c>
       <c r="B26" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>128813944</v>
       </c>
       <c r="B27" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128813543</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>128814795</v>
       </c>
       <c r="B29" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128814801</v>
       </c>
       <c r="B30" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128814805</v>
       </c>
       <c r="B31" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>128814494</v>
       </c>
       <c r="B32" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128814762</v>
       </c>
       <c r="B33" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128813918</v>
       </c>
       <c r="B34" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128813958</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>128826818</v>
       </c>
       <c r="B36" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -2332,7 +2332,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814567</v>
+        <v>128813792</v>
       </c>
       <c r="B16" t="n">
         <v>98678</v>
@@ -2371,14 +2371,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>321649</v>
+        <v>321756</v>
       </c>
       <c r="R16" t="n">
-        <v>6581085</v>
+        <v>6581052</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128813792</v>
+        <v>128814567</v>
       </c>
       <c r="B17" t="n">
         <v>98678</v>
@@ -2482,14 +2482,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>321756</v>
+        <v>321649</v>
       </c>
       <c r="R17" t="n">
-        <v>6581052</v>
+        <v>6581085</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128813875</v>
+        <v>128813533</v>
       </c>
       <c r="B25" t="n">
         <v>98678</v>
@@ -3384,14 +3384,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>321541</v>
+        <v>321778</v>
       </c>
       <c r="R25" t="n">
-        <v>6581033</v>
+        <v>6581074</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128813533</v>
+        <v>128813875</v>
       </c>
       <c r="B26" t="n">
         <v>98678</v>
@@ -3495,14 +3495,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>321778</v>
+        <v>321541</v>
       </c>
       <c r="R26" t="n">
-        <v>6581074</v>
+        <v>6581033</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -2776,53 +2776,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128813491</v>
+        <v>128812572</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>321933</v>
+        <v>321691</v>
       </c>
       <c r="R20" t="n">
-        <v>6581182</v>
+        <v>6581080</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2869,7 +2868,22 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2887,52 +2901,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128812572</v>
+        <v>128813491</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>321691</v>
+        <v>321933</v>
       </c>
       <c r="R21" t="n">
-        <v>6581080</v>
+        <v>6581182</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2979,22 +2994,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -1304,7 +1304,7 @@
         <v>128813827</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>128813503</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128813811</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128812360</v>
       </c>
       <c r="B10" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128814748</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128814786</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>128813685</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128813559</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128813792</v>
+        <v>128814567</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,14 +2371,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>321756</v>
+        <v>321649</v>
       </c>
       <c r="R16" t="n">
-        <v>6581052</v>
+        <v>6581085</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2443,10 +2443,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128814567</v>
+        <v>128813792</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,14 +2482,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>321649</v>
+        <v>321756</v>
       </c>
       <c r="R17" t="n">
-        <v>6581085</v>
+        <v>6581052</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2557,7 +2557,7 @@
         <v>128813756</v>
       </c>
       <c r="B18" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,53 +2665,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128813609</v>
+        <v>128812572</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>321774</v>
+        <v>321691</v>
       </c>
       <c r="R19" t="n">
-        <v>6581096</v>
+        <v>6581080</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2758,7 +2757,22 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2776,52 +2790,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128812572</v>
+        <v>128813609</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>321691</v>
+        <v>321774</v>
       </c>
       <c r="R20" t="n">
-        <v>6581080</v>
+        <v>6581096</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2868,22 +2883,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         <v>128813491</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128814510</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>128813781</v>
       </c>
       <c r="B23" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128813570</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3345,10 +3345,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128813533</v>
+        <v>128813875</v>
       </c>
       <c r="B25" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,14 +3384,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>321778</v>
+        <v>321541</v>
       </c>
       <c r="R25" t="n">
-        <v>6581074</v>
+        <v>6581033</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128813875</v>
+        <v>128813533</v>
       </c>
       <c r="B26" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,14 +3495,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>321541</v>
+        <v>321778</v>
       </c>
       <c r="R26" t="n">
-        <v>6581033</v>
+        <v>6581074</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3570,7 +3570,7 @@
         <v>128813944</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128813543</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>128814795</v>
       </c>
       <c r="B29" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128814801</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128814805</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>128814494</v>
       </c>
       <c r="B32" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128814762</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128813918</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128813958</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -1304,7 +1304,7 @@
         <v>128813827</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>128813503</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128813811</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128812360</v>
       </c>
       <c r="B10" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128814748</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128814786</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>128813685</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128813559</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,41 +2207,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128812889</v>
+        <v>128814567</v>
       </c>
       <c r="B15" t="n">
-        <v>79660</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2249,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>321697</v>
+        <v>321649</v>
       </c>
       <c r="R15" t="n">
-        <v>6581046</v>
+        <v>6581085</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2299,22 +2300,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Ljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Brandstubbe # Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2332,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814567</v>
+        <v>128813792</v>
       </c>
       <c r="B16" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,14 +2357,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen O, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>321649</v>
+        <v>321756</v>
       </c>
       <c r="R16" t="n">
-        <v>6581085</v>
+        <v>6581052</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2443,53 +2429,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128813792</v>
+        <v>128812889</v>
       </c>
       <c r="B17" t="n">
-        <v>98704</v>
+        <v>79660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skansen O, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>321756</v>
+        <v>321697</v>
       </c>
       <c r="R17" t="n">
-        <v>6581052</v>
+        <v>6581046</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2536,7 +2521,22 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Ljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Brandstubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2557,7 +2557,7 @@
         <v>128813756</v>
       </c>
       <c r="B18" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>128813609</v>
       </c>
       <c r="B20" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>128813491</v>
       </c>
       <c r="B21" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128814510</v>
       </c>
       <c r="B22" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>128813781</v>
       </c>
       <c r="B23" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128813570</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128813875</v>
       </c>
       <c r="B25" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>128813533</v>
       </c>
       <c r="B26" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>128813944</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128813543</v>
       </c>
       <c r="B28" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>128814795</v>
       </c>
       <c r="B29" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128814801</v>
       </c>
       <c r="B30" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128814805</v>
       </c>
       <c r="B31" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>128814494</v>
       </c>
       <c r="B32" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>128814762</v>
       </c>
       <c r="B33" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128813918</v>
       </c>
       <c r="B34" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128813958</v>
       </c>
       <c r="B35" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4697,6 +4697,450 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129923057</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Möreviksbäcken, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>321971</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6581191</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>S-Årj-0454</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129923063</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Möreviksbäcken, S om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>321647</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6581083</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>S-Årj-0449</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129923061</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Möreviksbäcken, S om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>321753</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6581056</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>S-Årj-0450</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129923058</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Möreviksbäcken, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>321930</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6581184</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>S-Årj-0453</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>129923057</v>
       </c>
       <c r="B37" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129923063</v>
       </c>
       <c r="B38" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>129923061</v>
       </c>
       <c r="B39" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>129923058</v>
       </c>
       <c r="B40" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>129923057</v>
       </c>
       <c r="B37" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129923063</v>
       </c>
       <c r="B38" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>129923061</v>
       </c>
       <c r="B39" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>129923058</v>
       </c>
       <c r="B40" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>129923057</v>
       </c>
       <c r="B37" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129923063</v>
       </c>
       <c r="B38" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>129923061</v>
       </c>
       <c r="B39" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>129923058</v>
       </c>
       <c r="B40" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>129923057</v>
       </c>
       <c r="B37" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129923063</v>
       </c>
       <c r="B38" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>129923061</v>
       </c>
       <c r="B39" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>129923058</v>
       </c>
       <c r="B40" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>129923057</v>
       </c>
       <c r="B37" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129923063</v>
       </c>
       <c r="B38" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>129923061</v>
       </c>
       <c r="B39" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>129923058</v>
       </c>
       <c r="B40" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 56535-2023 artfynd.xlsx
+++ b/artfynd/A 56535-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>129923057</v>
       </c>
       <c r="B37" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129923063</v>
       </c>
       <c r="B38" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>129923061</v>
       </c>
       <c r="B39" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>129923058</v>
       </c>
       <c r="B40" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
